--- a/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>23.2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>23.59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>22.6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>24.1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>22.3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>22.8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>22.8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>19.9</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>21.9</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25">
-        <v>23.2</v>
+      <c r="D25" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>23.2</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27">
-        <v>22.6</v>
+      <c r="D27" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>22.5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>22.1</v>
+      <c r="D29" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>23.59</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>19.4</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>23.1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>20.9</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>22.6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>21.9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>22.5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>22.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +833,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -806,7 +806,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -834,7 +834,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Avg_Temperature_timeseries.xlsx
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
